--- a/KiCAD/APEDSK-AU-BOM.xlsx
+++ b/KiCAD/APEDSK-AU-BOM.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
     <t>1N5711</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t>any reasonably close value should work fine (i.e. 4.7K)</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>wire link does work as well</t>
   </si>
 </sst>
 </file>
@@ -475,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="1" bestFit="1" customWidth="1"/>
@@ -616,65 +625,79 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C16" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="5">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4"/>
+      <c r="C17" s="5">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
